--- a/output/pdf_financials_xlsx/NTAR.xlsx
+++ b/output/pdf_financials_xlsx/NTAR.xlsx
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>14.166972</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>20.301785</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>21.29786</v>
       </c>
     </row>
     <row r="93">
@@ -3270,7 +3270,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>14.166972</v>
       </c>

--- a/output/pdf_financials_xlsx/NTAR.xlsx
+++ b/output/pdf_financials_xlsx/NTAR.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.907847</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.034771</v>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.907847</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.035022</v>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.453571</v>
+        <v>0.545724</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.290975</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">

--- a/output/pdf_financials_xlsx/NTAR.xlsx
+++ b/output/pdf_financials_xlsx/NTAR.xlsx
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.193513</v>
+        <v>2.105689</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.090267</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-25.520843</v>
+        <v>-25.608667</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-14.133551</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1763.658433768244</v>
+        <v>-1769.727650928792</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-647.2209234753947</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>2.105689</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">

--- a/output/pdf_financials_xlsx/NTAR.xlsx
+++ b/output/pdf_financials_xlsx/NTAR.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-27.714356</v>
+        <v>-27.684382</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-14.223818</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.029974</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-27.714356</v>
+        <v>-27.261542</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-14.223818</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.452814</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-27.714356</v>
+        <v>-27.684382</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-14.223818</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-25.608667</v>
+        <v>-25.578693</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-14.133551</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1769.727650928792</v>
+        <v>-1767.65625</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-647.2209234753947</v>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1082704320435977</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>2.380792</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.714545</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.588343</v>
       </c>
     </row>
     <row r="65">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.150668</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.474993</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.10366</v>
       </c>
     </row>
     <row r="68">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.22725</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07747</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.22725</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07747</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-13.343656</v>
+        <v>-13.570906</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.992178</v>
+        <v>-5.069648</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-2.839496</v>
@@ -4504,7 +4504,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>-0.22725</v>
       </c>
@@ -7164,7 +7168,11 @@
           <t>Deferred income tax recovery 17</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -7894,7 +7902,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E173" s="5" t="n">
         <v>0.029974</v>
       </c>
@@ -7925,7 +7937,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="n">
         <v>-27.261542</v>
       </c>
@@ -7954,7 +7970,11 @@
           <t>Net loss from discontinued operations 7</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
         <v>-0.452814</v>
       </c>
